--- a/artfynd/A 51811-2022 artfynd.xlsx
+++ b/artfynd/A 51811-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118627643</v>
+        <v>118627952</v>
       </c>
       <c r="B2" t="n">
-        <v>90500</v>
+        <v>78484</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,38 +691,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Hamnträsket (Stora Hamnträsket), Vb</t>
@@ -764,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118627952</v>
+        <v>118627643</v>
       </c>
       <c r="B3" t="n">
-        <v>78484</v>
+        <v>90500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,24 +808,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stora Hamnträsket (Stora Hamnträsket), Vb</t>
@@ -876,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118627749</v>
+        <v>118627544</v>
       </c>
       <c r="B4" t="n">
-        <v>57290</v>
+        <v>57306</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,16 +934,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -962,17 +962,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stora Hamnträsket (Stora Hamnträsket), Vb</t>
+          <t>Stora Hamnträsket, Ostträsket, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>792048</v>
+        <v>792069</v>
       </c>
       <c r="R4" t="n">
         <v>7209852</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1011,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosöksspår på äldre gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118627544</v>
+        <v>118627749</v>
       </c>
       <c r="B5" t="n">
-        <v>57306</v>
+        <v>57290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,16 +1059,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1082,17 +1087,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stora Hamnträsket, Ostträsket, Vb</t>
+          <t>Stora Hamnträsket (Stora Hamnträsket), Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>792069</v>
+        <v>792048</v>
       </c>
       <c r="R5" t="n">
         <v>7209852</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1121,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,12 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Födosöksspår på äldre gran</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 51811-2022 artfynd.xlsx
+++ b/artfynd/A 51811-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118627952</v>
+        <v>118627643</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>90507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,24 +691,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Hamnträsket (Stora Hamnträsket), Vb</t>
@@ -750,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118627643</v>
+        <v>118627952</v>
       </c>
       <c r="B3" t="n">
-        <v>90500</v>
+        <v>78491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,38 +817,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stora Hamnträsket (Stora Hamnträsket), Vb</t>
@@ -881,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118627544</v>
+        <v>118627749</v>
       </c>
       <c r="B4" t="n">
-        <v>57306</v>
+        <v>57290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,16 +934,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -962,17 +962,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stora Hamnträsket, Ostträsket, Vb</t>
+          <t>Stora Hamnträsket (Stora Hamnträsket), Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>792069</v>
+        <v>792048</v>
       </c>
       <c r="R4" t="n">
         <v>7209852</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,12 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosöksspår på äldre gran</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118627749</v>
+        <v>118627544</v>
       </c>
       <c r="B5" t="n">
-        <v>57290</v>
+        <v>57306</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,16 +1054,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1087,17 +1082,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stora Hamnträsket (Stora Hamnträsket), Vb</t>
+          <t>Stora Hamnträsket, Ostträsket, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>792048</v>
+        <v>792069</v>
       </c>
       <c r="R5" t="n">
         <v>7209852</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1126,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1131,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Födosöksspår på äldre gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,6 +1160,113 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118944766</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5166</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stora Hamnträsket, Ostträsket, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>792069</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7209852</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51811-2022 artfynd.xlsx
+++ b/artfynd/A 51811-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118627643</v>
+        <v>118627952</v>
       </c>
       <c r="B2" t="n">
-        <v>90507</v>
+        <v>78491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,38 +691,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Hamnträsket (Stora Hamnträsket), Vb</t>
@@ -764,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118627952</v>
+        <v>118627643</v>
       </c>
       <c r="B3" t="n">
-        <v>78491</v>
+        <v>90507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,24 +808,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stora Hamnträsket (Stora Hamnträsket), Vb</t>
@@ -876,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 51811-2022 artfynd.xlsx
+++ b/artfynd/A 51811-2022 artfynd.xlsx
@@ -898,7 +898,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>

--- a/artfynd/A 51811-2022 artfynd.xlsx
+++ b/artfynd/A 51811-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118627952</v>
+        <v>118627643</v>
       </c>
       <c r="B2" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,27 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stora Hamnträsket (Stora Hamnträsket), Vb</t>
+          <t>Stora Hamnträsket, Stora Hamnträsket, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,19 +769,14 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -792,57 +796,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118627643</v>
+        <v>118627952</v>
       </c>
       <c r="B3" t="n">
-        <v>90509</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stora Hamnträsket (Stora Hamnträsket), Vb</t>
+          <t>Stora Hamnträsket, Stora Hamnträsket, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -881,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,14 +876,19 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -918,32 +908,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118627749</v>
+        <v>118627544</v>
       </c>
       <c r="B4" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -962,17 +947,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stora Hamnträsket (Stora Hamnträsket), Vb</t>
+          <t>Stora Hamnträsket, Ostträsket, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>792048</v>
+        <v>792069</v>
       </c>
       <c r="R4" t="n">
         <v>7209852</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +996,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosöksspår på äldre gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,15 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118627544</v>
+        <v>118627749</v>
       </c>
       <c r="B5" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,16 +1039,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1082,17 +1067,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stora Hamnträsket, Ostträsket, Vb</t>
+          <t>Stora Hamnträsket, Stora Hamnträsket, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>792069</v>
+        <v>792048</v>
       </c>
       <c r="R5" t="n">
         <v>7209852</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1121,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,12 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Födosöksspår på äldre gran</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,12 +1146,7 @@
         <v>118944766</v>
       </c>
       <c r="B6" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 51811-2022 artfynd.xlsx
+++ b/artfynd/A 51811-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118627643</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118627952</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118627544</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118627749</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,8 +1267,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118944766</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>